--- a/config_beneficios.xlsx
+++ b/config_beneficios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Apps\Nueva carpeta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9891CE0-45EB-45A5-8305-7BA6CB4C4305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F382BEE8-842F-4629-99B2-D2B32A1D86E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-4815" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,22 +35,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>Nombre del modelo (Macro)</t>
-  </si>
-  <si>
-    <t>Dto. Base (%)</t>
-  </si>
-  <si>
-    <t>Dto. por Unidad Vieja (%)</t>
-  </si>
-  <si>
-    <t>Tope Máximo Dto. (%)</t>
-  </si>
-  <si>
     <t>Arrancador A400 REDSTRIPE</t>
   </si>
   <si>
     <t>Juego de llaves combinadas</t>
+  </si>
+  <si>
+    <t>Familia</t>
+  </si>
+  <si>
+    <t>Dto. Base</t>
+  </si>
+  <si>
+    <t>Dto. por Unidad</t>
+  </si>
+  <si>
+    <t>Tope</t>
   </si>
 </sst>
 </file>
@@ -353,23 +353,23 @@
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="B2" s="2">
         <v>5</v>
@@ -381,9 +381,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2">
         <v>10</v>

--- a/config_beneficios.xlsx
+++ b/config_beneficios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Apps\Nueva carpeta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E412B21-7F23-4E11-BF11-5A4D7D726187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C2190B-6E97-40FB-AED0-5FCD2CD8A061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4815" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan Canje Herramientas Lógica " sheetId="1" r:id="rId1"/>
@@ -42,9 +42,6 @@
   </si>
   <si>
     <t>Tope</t>
-  </si>
-  <si>
-    <t>Nombre Comercial</t>
   </si>
   <si>
     <t>Pinzas y Alicates</t>
@@ -102,6 +99,9 @@
   </si>
   <si>
     <t>Kits y Juegos de Herramientas</t>
+  </si>
+  <si>
+    <t>Nombres Comerciales</t>
   </si>
 </sst>
 </file>
@@ -186,10 +186,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -422,10 +422,10 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -439,10 +439,10 @@
     </row>
     <row r="2" spans="1:8" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2">
         <v>15</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="3" spans="1:8" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2">
         <v>2</v>
@@ -473,10 +473,10 @@
     </row>
     <row r="4" spans="1:8" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -490,10 +490,10 @@
     </row>
     <row r="5" spans="1:8" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
@@ -507,10 +507,10 @@
     </row>
     <row r="6" spans="1:8" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="2">
         <v>5</v>
@@ -524,10 +524,10 @@
     </row>
     <row r="7" spans="1:8" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2">
         <v>5</v>
@@ -541,10 +541,10 @@
     </row>
     <row r="8" spans="1:8" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2">
         <v>8</v>
@@ -558,10 +558,10 @@
     </row>
     <row r="9" spans="1:8" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="2">
         <v>8</v>
@@ -575,10 +575,10 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="2">
         <v>5</v>
@@ -594,10 +594,10 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="2">
         <v>10</v>

--- a/config_beneficios.xlsx
+++ b/config_beneficios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Apps\Nueva carpeta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C2190B-6E97-40FB-AED0-5FCD2CD8A061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599EFDFA-C662-4EB3-8DE8-522561509B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -445,10 +445,10 @@
         <v>14</v>
       </c>
       <c r="C2" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2">
         <v>30</v>
@@ -462,10 +462,10 @@
         <v>12</v>
       </c>
       <c r="C3" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2">
         <v>15</v>
@@ -479,10 +479,10 @@
         <v>15</v>
       </c>
       <c r="C4" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2">
         <v>15</v>
@@ -496,10 +496,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2">
         <v>15</v>
@@ -513,10 +513,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2">
         <v>15</v>
@@ -530,10 +530,10 @@
         <v>16</v>
       </c>
       <c r="C7" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2">
         <v>15</v>
@@ -547,10 +547,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2">
         <v>20</v>
@@ -564,10 +564,10 @@
         <v>18</v>
       </c>
       <c r="C9" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2">
         <v>20</v>
@@ -581,10 +581,10 @@
         <v>19</v>
       </c>
       <c r="C10" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2">
         <v>15</v>
@@ -600,10 +600,10 @@
         <v>21</v>
       </c>
       <c r="C11" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E11" s="2">
         <v>25</v>
